--- a/r5-aist-trustworthyai-poc-pipeline/StructureDefinition-eu-ai-provenance.xlsx
+++ b/r5-aist-trustworthyai-poc-pipeline/StructureDefinition-eu-ai-provenance.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$71</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2618" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2655" uniqueCount="448">
   <si>
     <t>Property</t>
   </si>
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>EU AI Act Provenance (Human-in-the-Loop)</t>
+    <t>EU AI Provenance</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T09:07:35+00:00</t>
+    <t>2026-06-18T11:52:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Records the execution of an AI system, including human oversight and data provenance.</t>
+    <t>A Provenance profile linking an AI-generated output to the contributing AI system, source data, and relevant processing or governance context.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -480,6 +480,22 @@
     <t>Categorizes the data processing as Primary Care or Secondary Use according to the EHDS.</t>
   </si>
   <si>
+    <t>Provenance.extension:secondaryUsePurpose</t>
+  </si>
+  <si>
+    <t>secondaryUsePurpose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/fhir/eu-ai-transparency/StructureDefinition/ehds-secondary-use-purpose}
+</t>
+  </si>
+  <si>
+    <t>EHDS Secondary Use Purpose</t>
+  </si>
+  <si>
+    <t>Documents the permitted purpose for secondary use of electronic health data under the EHDS.</t>
+  </si>
+  <si>
     <t>Provenance.extension:dataPermit</t>
   </si>
   <si>
@@ -654,6 +670,9 @@
   <si>
     <t xml:space="preserve">PurposeOfEvent
 </t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableReference
@@ -1697,12 +1716,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO70"/>
+  <dimension ref="A1:AO71"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="56.2421875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.3125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.81640625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="18.3125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -2932,7 +2951,7 @@
         <v>77</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>90</v>
@@ -3031,48 +3050,46 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>135</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="D12" t="s" s="2">
-        <v>154</v>
+        <v>18</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="N12" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="O12" t="s" s="2">
-        <v>158</v>
-      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>18</v>
       </c>
@@ -3120,7 +3137,7 @@
         <v>18</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -3141,7 +3158,7 @@
         <v>18</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>134</v>
+        <v>18</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>18</v>
@@ -3150,46 +3167,48 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H13" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I13" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="I13" t="s" s="2">
-        <v>18</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="O13" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="N13" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>18</v>
       </c>
@@ -3237,10 +3256,10 @@
         <v>18</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="AH13" t="s" s="2">
         <v>78</v>
@@ -3249,30 +3268,30 @@
         <v>18</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>166</v>
+        <v>134</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>167</v>
+        <v>18</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>168</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3283,7 +3302,7 @@
         <v>89</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>90</v>
@@ -3292,19 +3311,19 @@
         <v>18</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3354,13 +3373,13 @@
         <v>18</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>18</v>
@@ -3369,27 +3388,27 @@
         <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AM14" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AN14" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AO14" t="s" s="2">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="AL14" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" hidden="true">
-      <c r="A15" t="s" s="2">
-        <v>178</v>
-      </c>
       <c r="B15" t="s" s="2">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3397,31 +3416,31 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3471,7 +3490,7 @@
         <v>18</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -3486,27 +3505,27 @@
         <v>101</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>18</v>
+        <v>179</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>186</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3517,7 +3536,7 @@
         <v>77</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>18</v>
@@ -3526,19 +3545,19 @@
         <v>18</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>103</v>
+        <v>184</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3588,13 +3607,13 @@
         <v>18</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>18</v>
@@ -3606,24 +3625,24 @@
         <v>18</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>18</v>
+        <v>188</v>
       </c>
       <c r="AM16" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AN16" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AO16" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>192</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3634,7 +3653,7 @@
         <v>77</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>18</v>
@@ -3646,15 +3665,17 @@
         <v>18</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="M17" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>18</v>
@@ -3703,13 +3724,13 @@
         <v>18</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>18</v>
@@ -3718,41 +3739,41 @@
         <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM17" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AN17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AO17" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>201</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>203</v>
+        <v>18</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>18</v>
@@ -3761,18 +3782,16 @@
         <v>18</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="N18" s="2"/>
-      <c r="O18" t="s" s="2">
-        <v>207</v>
-      </c>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>18</v>
       </c>
@@ -3796,35 +3815,37 @@
         <v>18</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>209</v>
+        <v>18</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>210</v>
+        <v>18</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="AC18" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>18</v>
+      </c>
       <c r="AD18" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>140</v>
+        <v>18</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>18</v>
@@ -3833,40 +3854,38 @@
         <v>101</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>216</v>
+        <v>206</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>218</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>89</v>
+        <v>209</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>90</v>
@@ -3878,17 +3897,17 @@
         <v>18</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>18</v>
@@ -3913,29 +3932,29 @@
         <v>18</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y19" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="Z19" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>18</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="AC19" s="2"/>
       <c r="AD19" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3950,41 +3969,43 @@
         <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>216</v>
+        <v>222</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="D20" t="s" s="2">
-        <v>18</v>
+        <v>208</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>18</v>
@@ -3993,16 +4014,18 @@
         <v>18</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>91</v>
+        <v>210</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
+      <c r="O20" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>18</v>
       </c>
@@ -4026,13 +4049,11 @@
         <v>18</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>18</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>18</v>
+        <v>225</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>18</v>
@@ -4050,53 +4071,53 @@
         <v>18</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>225</v>
+        <v>18</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>18</v>
+        <v>218</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>18</v>
+        <v>219</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>18</v>
+        <v>221</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>18</v>
+        <v>222</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>154</v>
+        <v>18</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>18</v>
@@ -4108,17 +4129,15 @@
         <v>18</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>136</v>
+        <v>91</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="M21" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>157</v>
-      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>18</v>
@@ -4155,40 +4174,40 @@
         <v>18</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="AC21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF21" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI21" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AD21" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AF21" t="s" s="2">
+      <c r="AJ21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AG21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI21" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ21" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK21" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>18</v>
@@ -4206,14 +4225,14 @@
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>18</v>
@@ -4222,18 +4241,20 @@
         <v>18</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="M22" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N22" s="2"/>
+      <c r="N22" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>18</v>
@@ -4270,16 +4291,16 @@
         <v>18</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>18</v>
+        <v>139</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>18</v>
+        <v>237</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="AF22" t="s" s="2">
         <v>238</v>
@@ -4288,13 +4309,13 @@
         <v>77</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>18</v>
@@ -4303,7 +4324,7 @@
         <v>18</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>134</v>
+        <v>232</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>18</v>
@@ -4325,7 +4346,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>89</v>
@@ -4337,16 +4358,16 @@
         <v>18</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>91</v>
+        <v>241</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4397,7 +4418,7 @@
         <v>18</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -4406,10 +4427,10 @@
         <v>89</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>225</v>
+        <v>18</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>18</v>
@@ -4418,7 +4439,7 @@
         <v>18</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>226</v>
+        <v>134</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>18</v>
@@ -4429,21 +4450,21 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>154</v>
+        <v>18</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>18</v>
@@ -4455,17 +4476,15 @@
         <v>18</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>136</v>
+        <v>91</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="M24" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>157</v>
-      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>18</v>
@@ -4502,40 +4521,40 @@
         <v>18</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="AC24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI24" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AD24" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AF24" t="s" s="2">
+      <c r="AJ24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AG24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI24" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ24" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK24" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>18</v>
@@ -4546,14 +4565,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4569,23 +4588,21 @@
         <v>18</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>245</v>
+        <v>136</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>249</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>18</v>
       </c>
@@ -4621,19 +4638,19 @@
         <v>18</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>18</v>
+        <v>139</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>18</v>
+        <v>237</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4645,7 +4662,7 @@
         <v>18</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>18</v>
@@ -4654,7 +4671,7 @@
         <v>18</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>251</v>
+        <v>232</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>18</v>
@@ -4665,10 +4682,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4679,7 +4696,7 @@
         <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>18</v>
@@ -4688,19 +4705,23 @@
         <v>18</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>91</v>
+        <v>251</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>222</v>
+        <v>252</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>18</v>
       </c>
@@ -4748,19 +4769,19 @@
         <v>18</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>225</v>
+        <v>18</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>18</v>
@@ -4769,7 +4790,7 @@
         <v>18</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>18</v>
@@ -4780,21 +4801,21 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>154</v>
+        <v>18</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>18</v>
@@ -4806,17 +4827,15 @@
         <v>18</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>136</v>
+        <v>91</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="M27" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>157</v>
-      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>18</v>
@@ -4853,40 +4872,40 @@
         <v>18</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="AC27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI27" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AD27" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AF27" t="s" s="2">
+      <c r="AJ27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AG27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI27" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ27" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK27" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>18</v>
@@ -4897,21 +4916,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>18</v>
@@ -4920,23 +4939,21 @@
         <v>18</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>258</v>
+        <v>235</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>18</v>
       </c>
@@ -4945,7 +4962,7 @@
         <v>18</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>262</v>
+        <v>18</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>18</v>
@@ -4972,31 +4989,31 @@
         <v>18</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>18</v>
+        <v>139</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>18</v>
+        <v>237</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>263</v>
+        <v>238</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>18</v>
@@ -5005,7 +5022,7 @@
         <v>18</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>264</v>
+        <v>232</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>18</v>
@@ -5016,10 +5033,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5027,7 +5044,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>89</v>
@@ -5042,18 +5059,20 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="O29" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="L29" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>18</v>
       </c>
@@ -5062,7 +5081,7 @@
         <v>18</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>18</v>
+        <v>268</v>
       </c>
       <c r="T29" t="s" s="2">
         <v>18</v>
@@ -5101,7 +5120,7 @@
         <v>18</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -5122,7 +5141,7 @@
         <v>18</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>18</v>
@@ -5133,10 +5152,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5159,18 +5178,18 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>109</v>
+        <v>273</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="N30" s="2"/>
-      <c r="O30" t="s" s="2">
-        <v>277</v>
-      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>18</v>
       </c>
@@ -5218,7 +5237,7 @@
         <v>18</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -5227,7 +5246,7 @@
         <v>89</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>279</v>
+        <v>18</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>101</v>
@@ -5239,7 +5258,7 @@
         <v>18</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>18</v>
@@ -5250,10 +5269,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5276,17 +5295,17 @@
         <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>267</v>
+        <v>109</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>18</v>
@@ -5335,7 +5354,7 @@
         <v>18</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5344,7 +5363,7 @@
         <v>89</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>101</v>
@@ -5356,7 +5375,7 @@
         <v>18</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>18</v>
@@ -5367,10 +5386,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="B32" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5393,19 +5412,17 @@
         <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="N32" s="2"/>
+      <c r="O32" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>18</v>
@@ -5454,7 +5471,7 @@
         <v>18</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5463,7 +5480,7 @@
         <v>89</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>18</v>
+        <v>285</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>101</v>
@@ -5475,7 +5492,7 @@
         <v>18</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>18</v>
@@ -5486,10 +5503,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5512,19 +5529,19 @@
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>267</v>
+        <v>296</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="N33" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>18</v>
@@ -5573,7 +5590,7 @@
         <v>18</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5594,7 +5611,7 @@
         <v>18</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>18</v>
@@ -5605,10 +5622,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5631,16 +5648,20 @@
         <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="N34" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="M34" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>18</v>
       </c>
@@ -5688,7 +5709,7 @@
         <v>18</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5709,7 +5730,7 @@
         <v>18</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>134</v>
+        <v>310</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>18</v>
@@ -5718,18 +5739,16 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
         <v>311</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="C35" t="s" s="2">
         <v>312</v>
       </c>
+      <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>203</v>
+        <v>18</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5739,27 +5758,25 @@
         <v>89</v>
       </c>
       <c r="H35" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J35" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I35" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J35" t="s" s="2">
-        <v>18</v>
-      </c>
       <c r="K35" t="s" s="2">
-        <v>204</v>
+        <v>313</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>205</v>
+        <v>314</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>206</v>
+        <v>315</v>
       </c>
       <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>207</v>
-      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>18</v>
       </c>
@@ -5783,11 +5800,13 @@
         <v>18</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y35" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>18</v>
+      </c>
       <c r="Z35" t="s" s="2">
-        <v>313</v>
+        <v>18</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>18</v>
@@ -5805,13 +5824,13 @@
         <v>18</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>202</v>
+        <v>316</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>18</v>
@@ -5820,41 +5839,43 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>212</v>
+        <v>18</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>213</v>
+        <v>18</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>214</v>
+        <v>134</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>215</v>
+        <v>18</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>216</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="C36" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>318</v>
+      </c>
       <c r="D36" t="s" s="2">
-        <v>18</v>
+        <v>208</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>18</v>
@@ -5863,16 +5884,18 @@
         <v>18</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>91</v>
+        <v>210</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>18</v>
       </c>
@@ -5896,13 +5919,11 @@
         <v>18</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>18</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>18</v>
+        <v>319</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>18</v>
@@ -5920,53 +5941,53 @@
         <v>18</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>225</v>
+        <v>18</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>18</v>
+        <v>218</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>18</v>
+        <v>219</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>18</v>
+        <v>221</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>18</v>
+        <v>222</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>154</v>
+        <v>18</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>18</v>
@@ -5978,17 +5999,15 @@
         <v>18</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>136</v>
+        <v>91</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="M37" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>157</v>
-      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>18</v>
@@ -6025,40 +6044,40 @@
         <v>18</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="AC37" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI37" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AD37" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AF37" t="s" s="2">
+      <c r="AJ37" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AG37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI37" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ37" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK37" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>18</v>
@@ -6069,21 +6088,21 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>234</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>18</v>
@@ -6092,18 +6111,20 @@
         <v>18</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="M38" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N38" s="2"/>
+      <c r="N38" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>18</v>
@@ -6140,16 +6161,16 @@
         <v>18</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>18</v>
+        <v>139</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>18</v>
+        <v>237</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="AF38" t="s" s="2">
         <v>238</v>
@@ -6158,13 +6179,13 @@
         <v>77</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>18</v>
@@ -6173,7 +6194,7 @@
         <v>18</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>134</v>
+        <v>232</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>18</v>
@@ -6184,7 +6205,7 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>240</v>
@@ -6195,7 +6216,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>89</v>
@@ -6207,16 +6228,16 @@
         <v>18</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>91</v>
+        <v>241</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6267,7 +6288,7 @@
         <v>18</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -6276,10 +6297,10 @@
         <v>89</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>225</v>
+        <v>18</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>18</v>
@@ -6288,7 +6309,7 @@
         <v>18</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>226</v>
+        <v>134</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>18</v>
@@ -6299,21 +6320,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>154</v>
+        <v>18</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>18</v>
@@ -6325,17 +6346,15 @@
         <v>18</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>136</v>
+        <v>91</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="M40" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>157</v>
-      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>18</v>
@@ -6372,40 +6391,40 @@
         <v>18</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="AC40" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI40" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AD40" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AF40" t="s" s="2">
+      <c r="AJ40" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AG40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>18</v>
@@ -6416,14 +6435,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6439,23 +6458,21 @@
         <v>18</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>245</v>
+        <v>136</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>249</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>18</v>
       </c>
@@ -6491,19 +6508,19 @@
         <v>18</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>18</v>
+        <v>139</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>18</v>
+        <v>237</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6515,7 +6532,7 @@
         <v>18</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>18</v>
@@ -6524,7 +6541,7 @@
         <v>18</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>251</v>
+        <v>232</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>18</v>
@@ -6535,10 +6552,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6549,7 +6566,7 @@
         <v>77</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>18</v>
@@ -6558,19 +6575,23 @@
         <v>18</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>91</v>
+        <v>251</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>222</v>
+        <v>252</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>18</v>
       </c>
@@ -6618,19 +6639,19 @@
         <v>18</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>225</v>
+        <v>18</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>18</v>
@@ -6639,7 +6660,7 @@
         <v>18</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>18</v>
@@ -6650,21 +6671,21 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>154</v>
+        <v>18</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>18</v>
@@ -6676,17 +6697,15 @@
         <v>18</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>136</v>
+        <v>91</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="M43" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>157</v>
-      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>18</v>
@@ -6723,40 +6742,40 @@
         <v>18</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="AC43" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI43" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AD43" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AF43" t="s" s="2">
+      <c r="AJ43" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AG43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>18</v>
@@ -6767,21 +6786,21 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>18</v>
@@ -6790,23 +6809,21 @@
         <v>18</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>258</v>
+        <v>235</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>18</v>
       </c>
@@ -6815,7 +6832,7 @@
         <v>18</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>323</v>
+        <v>18</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>18</v>
@@ -6842,31 +6859,31 @@
         <v>18</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>18</v>
+        <v>139</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>18</v>
+        <v>237</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>263</v>
+        <v>238</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>18</v>
@@ -6875,7 +6892,7 @@
         <v>18</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>264</v>
+        <v>232</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>18</v>
@@ -6886,10 +6903,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6897,7 +6914,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>89</v>
@@ -6912,18 +6929,20 @@
         <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="O45" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="L45" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>18</v>
       </c>
@@ -6932,7 +6951,7 @@
         <v>18</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>18</v>
+        <v>329</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>18</v>
@@ -6971,7 +6990,7 @@
         <v>18</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -6992,7 +7011,7 @@
         <v>18</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>18</v>
@@ -7003,10 +7022,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7029,18 +7048,18 @@
         <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>109</v>
+        <v>273</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="N46" s="2"/>
-      <c r="O46" t="s" s="2">
-        <v>277</v>
-      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>18</v>
       </c>
@@ -7088,7 +7107,7 @@
         <v>18</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -7097,7 +7116,7 @@
         <v>89</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>279</v>
+        <v>18</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>101</v>
@@ -7109,7 +7128,7 @@
         <v>18</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>18</v>
@@ -7120,10 +7139,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7146,17 +7165,17 @@
         <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>267</v>
+        <v>109</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>18</v>
@@ -7205,7 +7224,7 @@
         <v>18</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -7214,7 +7233,7 @@
         <v>89</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>101</v>
@@ -7226,7 +7245,7 @@
         <v>18</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>18</v>
@@ -7237,10 +7256,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7263,19 +7282,17 @@
         <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="N48" s="2"/>
+      <c r="O48" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>18</v>
@@ -7324,7 +7341,7 @@
         <v>18</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -7333,7 +7350,7 @@
         <v>89</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>18</v>
+        <v>285</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>101</v>
@@ -7345,7 +7362,7 @@
         <v>18</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>18</v>
@@ -7356,10 +7373,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7382,19 +7399,19 @@
         <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>267</v>
+        <v>296</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>18</v>
@@ -7443,7 +7460,7 @@
         <v>18</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7464,7 +7481,7 @@
         <v>18</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>18</v>
@@ -7475,10 +7492,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7501,16 +7518,20 @@
         <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="M50" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>18</v>
       </c>
@@ -7558,7 +7579,7 @@
         <v>18</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7579,7 +7600,7 @@
         <v>18</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>134</v>
+        <v>310</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>18</v>
@@ -7590,10 +7611,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>330</v>
+        <v>312</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7613,16 +7634,16 @@
         <v>18</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>235</v>
+        <v>313</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7649,13 +7670,13 @@
         <v>18</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>333</v>
+        <v>18</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>334</v>
+        <v>18</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>18</v>
@@ -7673,7 +7694,7 @@
         <v>18</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>330</v>
+        <v>316</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -7688,27 +7709,27 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>335</v>
+        <v>18</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>213</v>
+        <v>18</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>336</v>
+        <v>134</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>215</v>
+        <v>18</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>337</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7719,7 +7740,7 @@
         <v>77</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>18</v>
@@ -7731,13 +7752,13 @@
         <v>18</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>339</v>
+        <v>241</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7764,13 +7785,13 @@
         <v>18</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>18</v>
+        <v>214</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>18</v>
+        <v>339</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>18</v>
+        <v>340</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>18</v>
@@ -7788,13 +7809,13 @@
         <v>18</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>18</v>
@@ -7803,27 +7824,27 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>18</v>
+        <v>343</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7834,7 +7855,7 @@
         <v>77</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>18</v>
@@ -7846,18 +7867,16 @@
         <v>18</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="N53" s="2"/>
-      <c r="O53" t="s" s="2">
-        <v>346</v>
-      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>18</v>
       </c>
@@ -7905,13 +7924,13 @@
         <v>18</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>18</v>
@@ -7920,16 +7939,16 @@
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>348</v>
+        <v>219</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>350</v>
+        <v>221</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>18</v>
@@ -7937,10 +7956,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7963,16 +7982,18 @@
         <v>18</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="L54" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>18</v>
       </c>
@@ -8020,7 +8041,7 @@
         <v>18</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -8035,27 +8056,27 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>213</v>
+        <v>354</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>336</v>
+        <v>355</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>215</v>
+        <v>356</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8063,35 +8084,31 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="O55" t="s" s="2">
         <v>360</v>
       </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>18</v>
       </c>
@@ -8139,42 +8156,42 @@
         <v>18</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ55" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="AK55" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="56" hidden="true">
-      <c r="A56" t="s" s="2">
-        <v>367</v>
-      </c>
       <c r="B56" t="s" s="2">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8182,31 +8199,35 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>267</v>
+        <v>362</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>222</v>
+        <v>363</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+        <v>364</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>366</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>18</v>
       </c>
@@ -8254,53 +8275,53 @@
         <v>18</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>224</v>
+        <v>361</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>225</v>
+        <v>18</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>18</v>
+        <v>367</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>18</v>
+        <v>368</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>18</v>
+        <v>369</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>226</v>
+        <v>370</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>18</v>
+        <v>371</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>18</v>
+        <v>372</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>154</v>
+        <v>18</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>18</v>
@@ -8312,17 +8333,15 @@
         <v>18</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>136</v>
+        <v>273</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="M57" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>157</v>
-      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>18</v>
@@ -8371,28 +8390,28 @@
         <v>18</v>
       </c>
       <c r="AF57" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>18</v>
@@ -8403,14 +8422,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>370</v>
+        <v>159</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8423,26 +8442,24 @@
         <v>18</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K58" t="s" s="2">
         <v>136</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>371</v>
+        <v>235</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>372</v>
+        <v>236</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>18</v>
       </c>
@@ -8490,7 +8507,7 @@
         <v>18</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>373</v>
+        <v>238</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8511,7 +8528,7 @@
         <v>18</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>134</v>
+        <v>232</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>18</v>
@@ -8522,45 +8539,45 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>18</v>
+        <v>376</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>235</v>
+        <v>136</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>377</v>
+        <v>162</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>378</v>
+        <v>163</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>18</v>
@@ -8585,66 +8602,66 @@
         <v>18</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="Y59" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF59" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="Z59" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>374</v>
-      </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>381</v>
+        <v>18</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>382</v>
+        <v>134</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>383</v>
+        <v>18</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>384</v>
+        <v>18</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8655,7 +8672,7 @@
         <v>77</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>18</v>
@@ -8664,22 +8681,22 @@
         <v>18</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>18</v>
@@ -8704,13 +8721,13 @@
         <v>18</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>18</v>
@@ -8728,13 +8745,13 @@
         <v>18</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>18</v>
@@ -8743,27 +8760,27 @@
         <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>18</v>
+        <v>387</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>18</v>
+        <v>389</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8771,10 +8788,10 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>18</v>
@@ -8783,19 +8800,23 @@
         <v>18</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="O61" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="L61" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>18</v>
       </c>
@@ -8819,13 +8840,13 @@
         <v>18</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>18</v>
+        <v>214</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>18</v>
+        <v>396</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>18</v>
+        <v>397</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>18</v>
@@ -8843,42 +8864,42 @@
         <v>18</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AO61" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>18</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8886,7 +8907,7 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>89</v>
@@ -8898,16 +8919,16 @@
         <v>18</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8958,28 +8979,28 @@
         <v>18</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>18</v>
+        <v>405</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>18</v>
+        <v>406</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>18</v>
@@ -8988,12 +9009,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9001,28 +9022,28 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>356</v>
+        <v>409</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9073,16 +9094,16 @@
         <v>18</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>18</v>
+        <v>404</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>101</v>
@@ -9094,16 +9115,16 @@
         <v>18</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>411</v>
+        <v>18</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>412</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
         <v>413</v>
       </c>
@@ -9116,28 +9137,28 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>267</v>
+        <v>362</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>222</v>
+        <v>414</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>223</v>
+        <v>415</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9188,19 +9209,19 @@
         <v>18</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>224</v>
+        <v>413</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>225</v>
+        <v>18</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>18</v>
@@ -9209,32 +9230,32 @@
         <v>18</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>226</v>
+        <v>416</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>18</v>
+        <v>417</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>18</v>
+        <v>418</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>154</v>
+        <v>18</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>18</v>
@@ -9246,17 +9267,15 @@
         <v>18</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>136</v>
+        <v>273</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="M65" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>157</v>
-      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>18</v>
@@ -9305,28 +9324,28 @@
         <v>18</v>
       </c>
       <c r="AF65" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM65" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>18</v>
@@ -9337,14 +9356,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>370</v>
+        <v>159</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9357,26 +9376,24 @@
         <v>18</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K66" t="s" s="2">
         <v>136</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>371</v>
+        <v>235</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>372</v>
+        <v>236</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>18</v>
       </c>
@@ -9424,7 +9441,7 @@
         <v>18</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>373</v>
+        <v>238</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
@@ -9445,7 +9462,7 @@
         <v>18</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>134</v>
+        <v>232</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>18</v>
@@ -9456,42 +9473,46 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>18</v>
+        <v>376</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="J67" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>417</v>
+        <v>377</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>18</v>
       </c>
@@ -9500,7 +9521,7 @@
         <v>18</v>
       </c>
       <c r="S67" t="s" s="2">
-        <v>419</v>
+        <v>18</v>
       </c>
       <c r="T67" t="s" s="2">
         <v>18</v>
@@ -9515,13 +9536,13 @@
         <v>18</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>113</v>
+        <v>18</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>420</v>
+        <v>18</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>421</v>
+        <v>18</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>18</v>
@@ -9539,19 +9560,19 @@
         <v>18</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>416</v>
+        <v>379</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>18</v>
@@ -9560,21 +9581,21 @@
         <v>18</v>
       </c>
       <c r="AM67" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="AN67" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s" s="2">
-        <v>425</v>
-      </c>
       <c r="B68" t="s" s="2">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9588,7 +9609,7 @@
         <v>89</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>18</v>
@@ -9597,17 +9618,15 @@
         <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>426</v>
+        <v>109</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>429</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>18</v>
@@ -9617,7 +9636,7 @@
         <v>18</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>18</v>
+        <v>425</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>18</v>
@@ -9632,13 +9651,13 @@
         <v>18</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>18</v>
+        <v>113</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>18</v>
+        <v>426</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>18</v>
+        <v>427</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>18</v>
@@ -9656,7 +9675,7 @@
         <v>18</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>89</v>
@@ -9677,13 +9696,13 @@
         <v>18</v>
       </c>
       <c r="AM68" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AO68" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>168</v>
       </c>
     </row>
     <row r="69" hidden="true">
@@ -9699,10 +9718,10 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>18</v>
@@ -9711,19 +9730,19 @@
         <v>18</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>79</v>
+        <v>432</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9776,10 +9795,10 @@
         <v>431</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>18</v>
@@ -9794,13 +9813,13 @@
         <v>18</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>18</v>
+        <v>356</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>436</v>
+        <v>173</v>
       </c>
     </row>
     <row r="70" hidden="true">
@@ -9831,15 +9850,17 @@
         <v>18</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>18</v>
@@ -9915,11 +9936,126 @@
         <v>18</v>
       </c>
       <c r="AO70" t="s" s="2">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AO71" t="s" s="2">
         <v>18</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO70">
+  <autoFilter ref="A1:AO71">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9929,7 +10065,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI69">
+  <conditionalFormatting sqref="A2:AI70">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
